--- a/excel-files/NAVOTAS/SAN ROQUE ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/SAN ROQUE ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F568F93-7874-461C-ADCF-685A10AF884F}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E78E6FED-6E85-4948-A341-1054EC178BBB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -742,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3703,17 +3703,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>269</v>
+      </c>
+      <c r="D11" s="1">
+        <v>335</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3806,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3876,7 +3884,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3896,19 +3904,27 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="C22" s="1">
+        <v>303</v>
+      </c>
+      <c r="D22" s="1">
+        <v>457</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19.5">
@@ -3928,7 +3944,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3956,7 +3972,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3984,7 +4000,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
@@ -4000,7 +4016,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>303</v>
@@ -4012,7 +4028,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
@@ -4030,17 +4046,25 @@
       <c r="B27" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="C27" s="1">
+        <v>303</v>
+      </c>
+      <c r="D27" s="1">
+        <v>457</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1">
@@ -4070,17 +4094,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>303</v>
+      </c>
+      <c r="D29" s="1">
+        <v>457</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4098,19 +4130,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>314</v>
+      </c>
+      <c r="D31" s="1">
+        <v>385</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4118,7 +4158,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4180,17 +4220,25 @@
       <c r="B35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="C35" s="1">
+        <v>309</v>
+      </c>
+      <c r="D35" s="1">
+        <v>378</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4198,19 +4246,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>309</v>
+      </c>
+      <c r="D36" s="1">
+        <v>385</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4220,17 +4276,25 @@
       <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="1">
+        <v>309</v>
+      </c>
+      <c r="D37" s="1">
+        <v>385</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4240,17 +4304,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>309</v>
+      </c>
+      <c r="D38" s="1">
+        <v>385</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4288,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4308,7 +4380,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4388,7 +4460,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4478,7 +4550,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4498,7 +4570,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4578,7 +4650,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4668,7 +4740,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4688,7 +4760,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4768,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4858,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4878,7 +4950,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4958,7 +5030,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5048,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5068,7 +5140,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5148,7 +5220,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5395,15 +5467,17 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E98" name="Textbooks"/>
+    <protectedRange sqref="C1:E10 D11:E11 C12:E34 C39:E98 D35:E38" name="Textbooks"/>
     <protectedRange sqref="F1:F98" name="SOURCE"/>
+    <protectedRange sqref="C11" name="Textbooks_1"/>
+    <protectedRange sqref="C35:C38" name="Textbooks_2"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E91:E98 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E2:E6 E21:E29 E14:E19 E8:E12 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5416,7 +5490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5446,38 +5520,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5516,10 +5590,10 @@
       <c r="L2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5552,10 +5626,10 @@
       <c r="X2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5991,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6060,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6379,18 +6453,12 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2152</v>
       </c>
-      <c r="K16" s="5">
-        <v>2128</v>
-      </c>
-      <c r="L16" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="10"/>
-        <v>24</v>
+        <v>2152</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="11"/>
@@ -6462,12 +6530,18 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>2152</v>
       </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+      <c r="K17" s="5">
+        <v>2128</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>2152</v>
+        <v>24</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6586,7 +6660,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -6661,7 +6735,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>269</v>
@@ -7030,7 +7104,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>310</v>
@@ -7261,7 +7335,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>310</v>
@@ -7338,7 +7412,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>310</v>
@@ -7498,7 +7572,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7567,7 +7641,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7843,7 +7917,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8133,7 +8207,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>309</v>
@@ -8216,7 +8290,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>309</v>
@@ -8524,7 +8598,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>309</v>
@@ -8846,7 +8920,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8915,7 +8989,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9191,7 +9265,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9481,7 +9555,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9550,7 +9624,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9826,7 +9900,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10116,7 +10190,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10185,7 +10259,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10461,7 +10535,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10751,7 +10825,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10820,7 +10894,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11096,7 +11170,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11386,7 +11460,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11455,7 +11529,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11731,7 +11805,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13568,191 +13642,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C23:C31 C33:C41 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C14:C21 C43:C51" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 Q14:R21 W14:X21 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D14:F21 K14:L21 D23:F31 D43:F51" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 M3 Y14:Y110 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G14:G21 M14:M110 G23:G31 G43:G51" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 Q14:R21 W14:X21 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D14:F21 D23:F31 D43:F51 K14:L21" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 M3 Y14:Y110 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G14:G21 G23:G31 G43:G51 M14:M110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13765,10 +13659,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 F14:F21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 L14:L21 F33:F41 F23:F31 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 X112:X127 F103:F110 R103:R110 L103:L110 X103:X110 F43:F51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 X5:X12 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 L14:L21" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14:G21 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 M14:M110 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14:G21 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 G43:G51 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13784,7 +13678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13814,38 +13708,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13884,10 +13778,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13920,10 +13814,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -14280,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14349,7 +14243,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14847,7 +14741,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>269</v>
@@ -14930,7 +14824,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1">
         <v>269</v>
@@ -15290,7 +15184,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15511,7 +15405,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1">
         <v>310</v>
@@ -15594,7 +15488,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>310</v>
@@ -15747,7 +15641,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15816,7 +15710,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -16092,7 +15986,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16507,7 +16401,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16576,7 +16470,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16852,7 +16746,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17267,7 +17161,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>293</v>
@@ -17350,7 +17244,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1">
         <v>293</v>
@@ -17682,7 +17576,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -18127,7 +18021,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18196,7 +18090,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18472,7 +18366,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18887,7 +18781,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18956,7 +18850,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19232,7 +19126,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19647,7 +19541,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19716,7 +19610,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19992,7 +19886,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -20407,7 +20301,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20476,7 +20370,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20752,7 +20646,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -22225,186 +22119,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22422,8 +22136,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 M115:M122 G12:G19 S12:S19 M12:M19 M21:M29 Y12:Y19 G21:G29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 Y21:Y29 S55:S65 M55:M65 G55:G65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F21:F29 X31:X41 X43:X53 X67:X77 X79:X89 R63:R64 X91:X101 X103:X113 F12:F19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R91:R101 R103:R113 R12:R19 R3:R10 X12:X19 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F103:F113 F115:F122 R115:R122 L115:L122 X21:X29 R55 R57:R58 R60:R61 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{972BD46E-A6D3-4CCE-A42E-806655F83913}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
